--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F777"/>
+  <dimension ref="A1:F778"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -15930,6 +15930,26 @@
         <v>4394.91</v>
       </c>
     </row>
+    <row r="778" spans="1:6">
+      <c r="A778" s="1">
+        <v>776</v>
+      </c>
+      <c r="B778" s="2">
+        <v>46084</v>
+      </c>
+      <c r="C778">
+        <v>12957.47</v>
+      </c>
+      <c r="D778">
+        <v>223.24</v>
+      </c>
+      <c r="E778">
+        <v>5870.47</v>
+      </c>
+      <c r="F778">
+        <v>4448.76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F778"/>
+  <dimension ref="A1:F779"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -15950,6 +15950,26 @@
         <v>4448.76</v>
       </c>
     </row>
+    <row r="779" spans="1:6">
+      <c r="A779" s="1">
+        <v>777</v>
+      </c>
+      <c r="B779" s="2">
+        <v>46085</v>
+      </c>
+      <c r="C779">
+        <v>13259.22</v>
+      </c>
+      <c r="D779">
+        <v>236.1</v>
+      </c>
+      <c r="E779">
+        <v>5811.31</v>
+      </c>
+      <c r="F779">
+        <v>4446.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F779"/>
+  <dimension ref="A1:F780"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -15970,6 +15970,26 @@
         <v>4446.44</v>
       </c>
     </row>
+    <row r="780" spans="1:6">
+      <c r="A780" s="1">
+        <v>778</v>
+      </c>
+      <c r="B780" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C780">
+        <v>12590.95</v>
+      </c>
+      <c r="D780">
+        <v>203.37</v>
+      </c>
+      <c r="E780">
+        <v>5287.86</v>
+      </c>
+      <c r="F780">
+        <v>4179.76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F780"/>
+  <dimension ref="A1:F781"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -15990,6 +15990,26 @@
         <v>4179.76</v>
       </c>
     </row>
+    <row r="781" spans="1:6">
+      <c r="A781" s="1">
+        <v>779</v>
+      </c>
+      <c r="B781" s="2">
+        <v>46087</v>
+      </c>
+      <c r="C781">
+        <v>12942.76</v>
+      </c>
+      <c r="D781">
+        <v>218.17</v>
+      </c>
+      <c r="E781">
+        <v>5447.55</v>
+      </c>
+      <c r="F781">
+        <v>4291.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F781"/>
+  <dimension ref="A1:F782"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16010,6 +16010,26 @@
         <v>4291.17</v>
       </c>
     </row>
+    <row r="782" spans="1:6">
+      <c r="A782" s="1">
+        <v>780</v>
+      </c>
+      <c r="B782" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C782">
+        <v>12988.43</v>
+      </c>
+      <c r="D782">
+        <v>214.3</v>
+      </c>
+      <c r="E782">
+        <v>5468.62</v>
+      </c>
+      <c r="F782">
+        <v>4186.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F782"/>
+  <dimension ref="A1:F783"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16030,6 +16030,26 @@
         <v>4186.08</v>
       </c>
     </row>
+    <row r="783" spans="1:6">
+      <c r="A783" s="1">
+        <v>781</v>
+      </c>
+      <c r="B783" s="2">
+        <v>46092</v>
+      </c>
+      <c r="C783">
+        <v>12876.27</v>
+      </c>
+      <c r="D783">
+        <v>211.24</v>
+      </c>
+      <c r="E783">
+        <v>5397.23</v>
+      </c>
+      <c r="F783">
+        <v>4177.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F783"/>
+  <dimension ref="A1:F784"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16050,6 +16050,26 @@
         <v>4177.03</v>
       </c>
     </row>
+    <row r="784" spans="1:6">
+      <c r="A784" s="1">
+        <v>782</v>
+      </c>
+      <c r="B784" s="2">
+        <v>46093</v>
+      </c>
+      <c r="C784">
+        <v>13243.54</v>
+      </c>
+      <c r="D784">
+        <v>225.04</v>
+      </c>
+      <c r="E784">
+        <v>5651.07</v>
+      </c>
+      <c r="F784">
+        <v>4260.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F784"/>
+  <dimension ref="A1:F785"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16070,6 +16070,26 @@
         <v>4260.55</v>
       </c>
     </row>
+    <row r="785" spans="1:6">
+      <c r="A785" s="1">
+        <v>783</v>
+      </c>
+      <c r="B785" s="2">
+        <v>46094</v>
+      </c>
+      <c r="C785">
+        <v>13173.99</v>
+      </c>
+      <c r="D785">
+        <v>219.2</v>
+      </c>
+      <c r="E785">
+        <v>5605.25</v>
+      </c>
+      <c r="F785">
+        <v>4207.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F785"/>
+  <dimension ref="A1:F786"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16090,6 +16090,26 @@
         <v>4207.12</v>
       </c>
     </row>
+    <row r="786" spans="1:6">
+      <c r="A786" s="1">
+        <v>784</v>
+      </c>
+      <c r="B786" s="2">
+        <v>46095</v>
+      </c>
+      <c r="C786">
+        <v>13232.09</v>
+      </c>
+      <c r="D786">
+        <v>224.48</v>
+      </c>
+      <c r="E786">
+        <v>5545.5</v>
+      </c>
+      <c r="F786">
+        <v>4235.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F786"/>
+  <dimension ref="A1:F787"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16110,6 +16110,26 @@
         <v>4235.22</v>
       </c>
     </row>
+    <row r="787" spans="1:6">
+      <c r="A787" s="1">
+        <v>785</v>
+      </c>
+      <c r="B787" s="2">
+        <v>46098</v>
+      </c>
+      <c r="C787">
+        <v>13145.58</v>
+      </c>
+      <c r="D787">
+        <v>218.1</v>
+      </c>
+      <c r="E787">
+        <v>5412.39</v>
+      </c>
+      <c r="F787">
+        <v>4200.66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F787"/>
+  <dimension ref="A1:F788"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16130,6 +16130,26 @@
         <v>4200.66</v>
       </c>
     </row>
+    <row r="788" spans="1:6">
+      <c r="A788" s="1">
+        <v>786</v>
+      </c>
+      <c r="B788" s="2">
+        <v>46099</v>
+      </c>
+      <c r="C788">
+        <v>13153.81</v>
+      </c>
+      <c r="D788">
+        <v>207.9</v>
+      </c>
+      <c r="E788">
+        <v>5577.7</v>
+      </c>
+      <c r="F788">
+        <v>4216.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F788"/>
+  <dimension ref="A1:F789"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16150,6 +16150,26 @@
         <v>4216.19</v>
       </c>
     </row>
+    <row r="789" spans="1:6">
+      <c r="A789" s="1">
+        <v>787</v>
+      </c>
+      <c r="B789" s="2">
+        <v>46100</v>
+      </c>
+      <c r="C789">
+        <v>13407.69</v>
+      </c>
+      <c r="D789">
+        <v>214.38</v>
+      </c>
+      <c r="E789">
+        <v>5764.71</v>
+      </c>
+      <c r="F789">
+        <v>4353.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F789"/>
+  <dimension ref="A1:F790"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16170,6 +16170,26 @@
         <v>4353.6</v>
       </c>
     </row>
+    <row r="790" spans="1:6">
+      <c r="A790" s="1">
+        <v>788</v>
+      </c>
+      <c r="B790" s="2">
+        <v>46101</v>
+      </c>
+      <c r="C790">
+        <v>13283.27</v>
+      </c>
+      <c r="D790">
+        <v>214.39</v>
+      </c>
+      <c r="E790">
+        <v>5635.22</v>
+      </c>
+      <c r="F790">
+        <v>4235.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F790"/>
+  <dimension ref="A1:F791"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16190,6 +16190,26 @@
         <v>4235.96</v>
       </c>
     </row>
+    <row r="791" spans="1:6">
+      <c r="A791" s="1">
+        <v>789</v>
+      </c>
+      <c r="B791" s="2">
+        <v>46102</v>
+      </c>
+      <c r="C791">
+        <v>12423.72</v>
+      </c>
+      <c r="D791">
+        <v>188.23</v>
+      </c>
+      <c r="E791">
+        <v>5225.67</v>
+      </c>
+      <c r="F791">
+        <v>3883.47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F791"/>
+  <dimension ref="A1:F792"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16210,6 +16210,26 @@
         <v>3883.47</v>
       </c>
     </row>
+    <row r="792" spans="1:6">
+      <c r="A792" s="1">
+        <v>790</v>
+      </c>
+      <c r="B792" s="2">
+        <v>46105</v>
+      </c>
+      <c r="C792">
+        <v>12010.38</v>
+      </c>
+      <c r="D792">
+        <v>190.51</v>
+      </c>
+      <c r="E792">
+        <v>5206.85</v>
+      </c>
+      <c r="F792">
+        <v>3774.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F792"/>
+  <dimension ref="A1:F793"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16230,6 +16230,26 @@
         <v>3774.84</v>
       </c>
     </row>
+    <row r="793" spans="1:6">
+      <c r="A793" s="1">
+        <v>791</v>
+      </c>
+      <c r="B793" s="2">
+        <v>46106</v>
+      </c>
+      <c r="C793">
+        <v>11625.36</v>
+      </c>
+      <c r="D793">
+        <v>175</v>
+      </c>
+      <c r="E793">
+        <v>4927.36</v>
+      </c>
+      <c r="F793">
+        <v>3769.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F793"/>
+  <dimension ref="A1:F794"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16250,6 +16250,26 @@
         <v>3769.05</v>
       </c>
     </row>
+    <row r="794" spans="1:6">
+      <c r="A794" s="1">
+        <v>792</v>
+      </c>
+      <c r="B794" s="2">
+        <v>46107</v>
+      </c>
+      <c r="C794">
+        <v>11453.96</v>
+      </c>
+      <c r="D794">
+        <v>181.58</v>
+      </c>
+      <c r="E794">
+        <v>4910.08</v>
+      </c>
+      <c r="F794">
+        <v>3615.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F794"/>
+  <dimension ref="A1:F795"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16270,6 +16270,26 @@
         <v>3615.09</v>
       </c>
     </row>
+    <row r="795" spans="1:6">
+      <c r="A795" s="1">
+        <v>793</v>
+      </c>
+      <c r="B795" s="2">
+        <v>46108</v>
+      </c>
+      <c r="C795">
+        <v>12053.08</v>
+      </c>
+      <c r="D795">
+        <v>193.21</v>
+      </c>
+      <c r="E795">
+        <v>5149.14</v>
+      </c>
+      <c r="F795">
+        <v>3786.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F795"/>
+  <dimension ref="A1:F796"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16290,6 +16290,26 @@
         <v>3786.6</v>
       </c>
     </row>
+    <row r="796" spans="1:6">
+      <c r="A796" s="1">
+        <v>794</v>
+      </c>
+      <c r="B796" s="2">
+        <v>46109</v>
+      </c>
+      <c r="C796">
+        <v>11626.2</v>
+      </c>
+      <c r="D796">
+        <v>175.55</v>
+      </c>
+      <c r="E796">
+        <v>4875.94</v>
+      </c>
+      <c r="F796">
+        <v>3579.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F796"/>
+  <dimension ref="A1:F797"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16310,6 +16310,26 @@
         <v>3579.34</v>
       </c>
     </row>
+    <row r="797" spans="1:6">
+      <c r="A797" s="1">
+        <v>795</v>
+      </c>
+      <c r="B797" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C797">
+        <v>11772.54</v>
+      </c>
+      <c r="D797">
+        <v>177.2</v>
+      </c>
+      <c r="E797">
+        <v>4832.75</v>
+      </c>
+      <c r="F797">
+        <v>3625.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F797"/>
+  <dimension ref="A1:F798"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16330,6 +16330,26 @@
         <v>3625.21</v>
       </c>
     </row>
+    <row r="798" spans="1:6">
+      <c r="A798" s="1">
+        <v>796</v>
+      </c>
+      <c r="B798" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C798">
+        <v>11831.31</v>
+      </c>
+      <c r="D798">
+        <v>184.82</v>
+      </c>
+      <c r="E798">
+        <v>5015.54</v>
+      </c>
+      <c r="F798">
+        <v>3735.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F798"/>
+  <dimension ref="A1:F799"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16350,6 +16350,26 @@
         <v>3735.53</v>
       </c>
     </row>
+    <row r="799" spans="1:6">
+      <c r="A799" s="1">
+        <v>797</v>
+      </c>
+      <c r="B799" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C799">
+        <v>11945.31</v>
+      </c>
+      <c r="D799">
+        <v>188.41</v>
+      </c>
+      <c r="E799">
+        <v>4945.73</v>
+      </c>
+      <c r="F799">
+        <v>3753.36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F799"/>
+  <dimension ref="A1:F800"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16370,6 +16370,26 @@
         <v>3753.36</v>
       </c>
     </row>
+    <row r="800" spans="1:6">
+      <c r="A800" s="1">
+        <v>798</v>
+      </c>
+      <c r="B800" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C800">
+        <v>12239.75</v>
+      </c>
+      <c r="D800">
+        <v>193.37</v>
+      </c>
+      <c r="E800">
+        <v>5062.23</v>
+      </c>
+      <c r="F800">
+        <v>3801.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F800"/>
+  <dimension ref="A1:F801"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16390,6 +16390,26 @@
         <v>3801.84</v>
       </c>
     </row>
+    <row r="801" spans="1:6">
+      <c r="A801" s="1">
+        <v>799</v>
+      </c>
+      <c r="B801" s="2">
+        <v>46116</v>
+      </c>
+      <c r="C801">
+        <v>11892.3</v>
+      </c>
+      <c r="D801">
+        <v>181.97</v>
+      </c>
+      <c r="E801">
+        <v>4896.01</v>
+      </c>
+      <c r="F801">
+        <v>3750.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F801"/>
+  <dimension ref="A1:F802"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16410,6 +16410,26 @@
         <v>3750.19</v>
       </c>
     </row>
+    <row r="802" spans="1:6">
+      <c r="A802" s="1">
+        <v>800</v>
+      </c>
+      <c r="B802" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C802">
+        <v>11742.9</v>
+      </c>
+      <c r="D802">
+        <v>179.69</v>
+      </c>
+      <c r="E802">
+        <v>4834.5</v>
+      </c>
+      <c r="F802">
+        <v>3703.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F802"/>
+  <dimension ref="A1:F803"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16430,6 +16430,26 @@
         <v>3703.08</v>
       </c>
     </row>
+    <row r="803" spans="1:6">
+      <c r="A803" s="1">
+        <v>801</v>
+      </c>
+      <c r="B803" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C803">
+        <v>11746.17</v>
+      </c>
+      <c r="D803">
+        <v>179.74</v>
+      </c>
+      <c r="E803">
+        <v>4835.85</v>
+      </c>
+      <c r="F803">
+        <v>3704.11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F803"/>
+  <dimension ref="A1:F804"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16450,6 +16450,26 @@
         <v>3704.11</v>
       </c>
     </row>
+    <row r="804" spans="1:6">
+      <c r="A804" s="1">
+        <v>802</v>
+      </c>
+      <c r="B804" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C804">
+        <v>11610.14</v>
+      </c>
+      <c r="D804">
+        <v>181.53</v>
+      </c>
+      <c r="E804">
+        <v>4891.58</v>
+      </c>
+      <c r="F804">
+        <v>3683.16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F804"/>
+  <dimension ref="A1:F805"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16470,6 +16470,26 @@
         <v>3683.16</v>
       </c>
     </row>
+    <row r="805" spans="1:6">
+      <c r="A805" s="1">
+        <v>803</v>
+      </c>
+      <c r="B805" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C805">
+        <v>11993.37</v>
+      </c>
+      <c r="D805">
+        <v>192.2</v>
+      </c>
+      <c r="E805">
+        <v>5207.71</v>
+      </c>
+      <c r="F805">
+        <v>4001.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F805"/>
+  <dimension ref="A1:F806"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16490,6 +16490,26 @@
         <v>4001.5</v>
       </c>
     </row>
+    <row r="806" spans="1:6">
+      <c r="A806" s="1">
+        <v>804</v>
+      </c>
+      <c r="B806" s="2">
+        <v>46123</v>
+      </c>
+      <c r="C806">
+        <v>11786.09</v>
+      </c>
+      <c r="D806">
+        <v>183.31</v>
+      </c>
+      <c r="E806">
+        <v>5045.95</v>
+      </c>
+      <c r="F806">
+        <v>3830.86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F806"/>
+  <dimension ref="A1:F807"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16510,6 +16510,26 @@
         <v>3830.86</v>
       </c>
     </row>
+    <row r="807" spans="1:6">
+      <c r="A807" s="1">
+        <v>805</v>
+      </c>
+      <c r="B807" s="2">
+        <v>46126</v>
+      </c>
+      <c r="C807">
+        <v>11702.64</v>
+      </c>
+      <c r="D807">
+        <v>185.2</v>
+      </c>
+      <c r="E807">
+        <v>5054.9</v>
+      </c>
+      <c r="F807">
+        <v>3738.47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F807"/>
+  <dimension ref="A1:F808"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16530,6 +16530,26 @@
         <v>3738.47</v>
       </c>
     </row>
+    <row r="808" spans="1:6">
+      <c r="A808" s="1">
+        <v>806</v>
+      </c>
+      <c r="B808" s="2">
+        <v>46127</v>
+      </c>
+      <c r="C808">
+        <v>11517.29</v>
+      </c>
+      <c r="D808">
+        <v>181.36</v>
+      </c>
+      <c r="E808">
+        <v>4953.07</v>
+      </c>
+      <c r="F808">
+        <v>3726.39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F808"/>
+  <dimension ref="A1:F809"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16550,6 +16550,26 @@
         <v>3726.39</v>
       </c>
     </row>
+    <row r="809" spans="1:6">
+      <c r="A809" s="1">
+        <v>807</v>
+      </c>
+      <c r="B809" s="2">
+        <v>46128</v>
+      </c>
+      <c r="C809">
+        <v>11597.77</v>
+      </c>
+      <c r="D809">
+        <v>187.28</v>
+      </c>
+      <c r="E809">
+        <v>5019.11</v>
+      </c>
+      <c r="F809">
+        <v>3766.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F809"/>
+  <dimension ref="A1:F810"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16570,6 +16570,26 @@
         <v>3766.14</v>
       </c>
     </row>
+    <row r="810" spans="1:6">
+      <c r="A810" s="1">
+        <v>808</v>
+      </c>
+      <c r="B810" s="2">
+        <v>46129</v>
+      </c>
+      <c r="C810">
+        <v>11798.75</v>
+      </c>
+      <c r="D810">
+        <v>192.21</v>
+      </c>
+      <c r="E810">
+        <v>5159.08</v>
+      </c>
+      <c r="F810">
+        <v>3865.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F810"/>
+  <dimension ref="A1:F811"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16590,6 +16590,26 @@
         <v>3865.03</v>
       </c>
     </row>
+    <row r="811" spans="1:6">
+      <c r="A811" s="1">
+        <v>809</v>
+      </c>
+      <c r="B811" s="2">
+        <v>46130</v>
+      </c>
+      <c r="C811">
+        <v>11721.19</v>
+      </c>
+      <c r="D811">
+        <v>194.84</v>
+      </c>
+      <c r="E811">
+        <v>5222.89</v>
+      </c>
+      <c r="F811">
+        <v>3863.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F811"/>
+  <dimension ref="A1:F812"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16610,6 +16610,26 @@
         <v>3863.38</v>
       </c>
     </row>
+    <row r="812" spans="1:6">
+      <c r="A812" s="1">
+        <v>810</v>
+      </c>
+      <c r="B812" s="2">
+        <v>46133</v>
+      </c>
+      <c r="C812">
+        <v>11781.37</v>
+      </c>
+      <c r="D812">
+        <v>191.87</v>
+      </c>
+      <c r="E812">
+        <v>5183.75</v>
+      </c>
+      <c r="F812">
+        <v>3855.76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F812"/>
+  <dimension ref="A1:F813"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16630,6 +16630,26 @@
         <v>3855.76</v>
       </c>
     </row>
+    <row r="813" spans="1:6">
+      <c r="A813" s="1">
+        <v>811</v>
+      </c>
+      <c r="B813" s="2">
+        <v>46134</v>
+      </c>
+      <c r="C813">
+        <v>11543.44</v>
+      </c>
+      <c r="D813">
+        <v>190.18</v>
+      </c>
+      <c r="E813">
+        <v>4966.49</v>
+      </c>
+      <c r="F813">
+        <v>3714.68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F813"/>
+  <dimension ref="A1:F814"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16650,6 +16650,26 @@
         <v>3714.68</v>
       </c>
     </row>
+    <row r="814" spans="1:6">
+      <c r="A814" s="1">
+        <v>812</v>
+      </c>
+      <c r="B814" s="2">
+        <v>46135</v>
+      </c>
+      <c r="C814">
+        <v>11518.12</v>
+      </c>
+      <c r="D814">
+        <v>190.5</v>
+      </c>
+      <c r="E814">
+        <v>5020.3</v>
+      </c>
+      <c r="F814">
+        <v>3773.67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F814"/>
+  <dimension ref="A1:F815"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16670,6 +16670,26 @@
         <v>3773.67</v>
       </c>
     </row>
+    <row r="815" spans="1:6">
+      <c r="A815" s="1">
+        <v>813</v>
+      </c>
+      <c r="B815" s="2">
+        <v>46136</v>
+      </c>
+      <c r="C815">
+        <v>11409.47</v>
+      </c>
+      <c r="D815">
+        <v>187.82</v>
+      </c>
+      <c r="E815">
+        <v>5009.28</v>
+      </c>
+      <c r="F815">
+        <v>3750.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F815"/>
+  <dimension ref="A1:F816"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16690,6 +16690,26 @@
         <v>3750.95</v>
       </c>
     </row>
+    <row r="816" spans="1:6">
+      <c r="A816" s="1">
+        <v>814</v>
+      </c>
+      <c r="B816" s="2">
+        <v>46137</v>
+      </c>
+      <c r="C816">
+        <v>11459.31</v>
+      </c>
+      <c r="D816">
+        <v>181.01</v>
+      </c>
+      <c r="E816">
+        <v>4926.93</v>
+      </c>
+      <c r="F816">
+        <v>3622.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F816"/>
+  <dimension ref="A1:F817"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16710,6 +16710,26 @@
         <v>3622.96</v>
       </c>
     </row>
+    <row r="817" spans="1:6">
+      <c r="A817" s="1">
+        <v>815</v>
+      </c>
+      <c r="B817" s="2">
+        <v>46140</v>
+      </c>
+      <c r="C817">
+        <v>11332.15</v>
+      </c>
+      <c r="D817">
+        <v>179.96</v>
+      </c>
+      <c r="E817">
+        <v>4800.65</v>
+      </c>
+      <c r="F817">
+        <v>3569.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F817"/>
+  <dimension ref="A1:F818"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16730,6 +16730,26 @@
         <v>3569.22</v>
       </c>
     </row>
+    <row r="818" spans="1:6">
+      <c r="A818" s="1">
+        <v>816</v>
+      </c>
+      <c r="B818" s="2">
+        <v>46141</v>
+      </c>
+      <c r="C818">
+        <v>11268.38</v>
+      </c>
+      <c r="D818">
+        <v>182.31</v>
+      </c>
+      <c r="E818">
+        <v>4790.97</v>
+      </c>
+      <c r="F818">
+        <v>3551.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F818"/>
+  <dimension ref="A1:F819"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16750,6 +16750,26 @@
         <v>3551.8</v>
       </c>
     </row>
+    <row r="819" spans="1:6">
+      <c r="A819" s="1">
+        <v>817</v>
+      </c>
+      <c r="B819" s="2">
+        <v>46142</v>
+      </c>
+      <c r="C819">
+        <v>10989.84</v>
+      </c>
+      <c r="D819">
+        <v>176.2</v>
+      </c>
+      <c r="E819">
+        <v>4680.11</v>
+      </c>
+      <c r="F819">
+        <v>3524.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F819"/>
+  <dimension ref="A1:F820"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16770,6 +16770,26 @@
         <v>3524.53</v>
       </c>
     </row>
+    <row r="820" spans="1:6">
+      <c r="A820" s="1">
+        <v>818</v>
+      </c>
+      <c r="B820" s="2">
+        <v>46143</v>
+      </c>
+      <c r="C820">
+        <v>10875.28</v>
+      </c>
+      <c r="D820">
+        <v>175.01</v>
+      </c>
+      <c r="E820">
+        <v>4576.56</v>
+      </c>
+      <c r="F820">
+        <v>3458.27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F820"/>
+  <dimension ref="A1:F821"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16790,6 +16790,26 @@
         <v>3458.27</v>
       </c>
     </row>
+    <row r="821" spans="1:6">
+      <c r="A821" s="1">
+        <v>819</v>
+      </c>
+      <c r="B821" s="2">
+        <v>46147</v>
+      </c>
+      <c r="C821">
+        <v>11246.39</v>
+      </c>
+      <c r="D821">
+        <v>177.39</v>
+      </c>
+      <c r="E821">
+        <v>4826.57</v>
+      </c>
+      <c r="F821">
+        <v>3708.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F821"/>
+  <dimension ref="A1:F822"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16810,6 +16810,26 @@
         <v>3708.45</v>
       </c>
     </row>
+    <row r="822" spans="1:6">
+      <c r="A822" s="1">
+        <v>820</v>
+      </c>
+      <c r="B822" s="2">
+        <v>46148</v>
+      </c>
+      <c r="C822">
+        <v>11232.38</v>
+      </c>
+      <c r="D822">
+        <v>177.17</v>
+      </c>
+      <c r="E822">
+        <v>4820.56</v>
+      </c>
+      <c r="F822">
+        <v>3703.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F822"/>
+  <dimension ref="A1:F823"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16830,6 +16830,26 @@
         <v>3703.83</v>
       </c>
     </row>
+    <row r="823" spans="1:6">
+      <c r="A823" s="1">
+        <v>821</v>
+      </c>
+      <c r="B823" s="2">
+        <v>46149</v>
+      </c>
+      <c r="C823">
+        <v>11069.11</v>
+      </c>
+      <c r="D823">
+        <v>177.6</v>
+      </c>
+      <c r="E823">
+        <v>4774.17</v>
+      </c>
+      <c r="F823">
+        <v>3659.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F823"/>
+  <dimension ref="A1:F824"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16850,6 +16850,26 @@
         <v>3659.23</v>
       </c>
     </row>
+    <row r="824" spans="1:6">
+      <c r="A824" s="1">
+        <v>822</v>
+      </c>
+      <c r="B824" s="2">
+        <v>46150</v>
+      </c>
+      <c r="C824">
+        <v>11292.4</v>
+      </c>
+      <c r="D824">
+        <v>186.21</v>
+      </c>
+      <c r="E824">
+        <v>4812.63</v>
+      </c>
+      <c r="F824">
+        <v>3675.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F824"/>
+  <dimension ref="A1:F825"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16870,6 +16870,26 @@
         <v>3675.45</v>
       </c>
     </row>
+    <row r="825" spans="1:6">
+      <c r="A825" s="1">
+        <v>823</v>
+      </c>
+      <c r="B825" s="2">
+        <v>46151</v>
+      </c>
+      <c r="C825">
+        <v>11330.34</v>
+      </c>
+      <c r="D825">
+        <v>191.91</v>
+      </c>
+      <c r="E825">
+        <v>4982.79</v>
+      </c>
+      <c r="F825">
+        <v>3654.68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F825"/>
+  <dimension ref="A1:F826"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16890,6 +16890,26 @@
         <v>3654.68</v>
       </c>
     </row>
+    <row r="826" spans="1:6">
+      <c r="A826" s="1">
+        <v>824</v>
+      </c>
+      <c r="B826" s="2">
+        <v>46155</v>
+      </c>
+      <c r="C826">
+        <v>11219.11</v>
+      </c>
+      <c r="D826">
+        <v>190.74</v>
+      </c>
+      <c r="E826">
+        <v>4917.84</v>
+      </c>
+      <c r="F826">
+        <v>3575.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F826"/>
+  <dimension ref="A1:F827"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16910,6 +16910,26 @@
         <v>3575.1</v>
       </c>
     </row>
+    <row r="827" spans="1:6">
+      <c r="A827" s="1">
+        <v>825</v>
+      </c>
+      <c r="B827" s="2">
+        <v>46156</v>
+      </c>
+      <c r="C827">
+        <v>11031.66</v>
+      </c>
+      <c r="D827">
+        <v>197.22</v>
+      </c>
+      <c r="E827">
+        <v>4989.52</v>
+      </c>
+      <c r="F827">
+        <v>3511.06</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F827"/>
+  <dimension ref="A1:F828"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16930,6 +16930,26 @@
         <v>3511.06</v>
       </c>
     </row>
+    <row r="828" spans="1:6">
+      <c r="A828" s="1">
+        <v>826</v>
+      </c>
+      <c r="B828" s="2">
+        <v>46157</v>
+      </c>
+      <c r="C828">
+        <v>10994.7</v>
+      </c>
+      <c r="D828">
+        <v>203.86</v>
+      </c>
+      <c r="E828">
+        <v>5001.55</v>
+      </c>
+      <c r="F828">
+        <v>3484.86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F828"/>
+  <dimension ref="A1:F829"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16950,6 +16950,26 @@
         <v>3484.86</v>
       </c>
     </row>
+    <row r="829" spans="1:6">
+      <c r="A829" s="1">
+        <v>827</v>
+      </c>
+      <c r="B829" s="2">
+        <v>46158</v>
+      </c>
+      <c r="C829">
+        <v>11010.33</v>
+      </c>
+      <c r="D829">
+        <v>204.04</v>
+      </c>
+      <c r="E829">
+        <v>4942.02</v>
+      </c>
+      <c r="F829">
+        <v>3434.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F829"/>
+  <dimension ref="A1:F830"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16970,6 +16970,26 @@
         <v>3434.96</v>
       </c>
     </row>
+    <row r="830" spans="1:6">
+      <c r="A830" s="1">
+        <v>828</v>
+      </c>
+      <c r="B830" s="2">
+        <v>46161</v>
+      </c>
+      <c r="C830">
+        <v>10532.56</v>
+      </c>
+      <c r="D830">
+        <v>183.16</v>
+      </c>
+      <c r="E830">
+        <v>4584.73</v>
+      </c>
+      <c r="F830">
+        <v>3303.06</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F830"/>
+  <dimension ref="A1:F831"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -16990,6 +16990,26 @@
         <v>3303.06</v>
       </c>
     </row>
+    <row r="831" spans="1:6">
+      <c r="A831" s="1">
+        <v>829</v>
+      </c>
+      <c r="B831" s="2">
+        <v>46162</v>
+      </c>
+      <c r="C831">
+        <v>10464.39</v>
+      </c>
+      <c r="D831">
+        <v>173.58</v>
+      </c>
+      <c r="E831">
+        <v>4524.62</v>
+      </c>
+      <c r="F831">
+        <v>3247.92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F831"/>
+  <dimension ref="A1:F832"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17010,6 +17010,26 @@
         <v>3247.92</v>
       </c>
     </row>
+    <row r="832" spans="1:6">
+      <c r="A832" s="1">
+        <v>830</v>
+      </c>
+      <c r="B832" s="2">
+        <v>46163</v>
+      </c>
+      <c r="C832">
+        <v>10257.52</v>
+      </c>
+      <c r="D832">
+        <v>173.46</v>
+      </c>
+      <c r="E832">
+        <v>4425.38</v>
+      </c>
+      <c r="F832">
+        <v>3150.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F832"/>
+  <dimension ref="A1:F833"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17030,6 +17030,26 @@
         <v>3150.23</v>
       </c>
     </row>
+    <row r="833" spans="1:6">
+      <c r="A833" s="1">
+        <v>831</v>
+      </c>
+      <c r="B833" s="2">
+        <v>46164</v>
+      </c>
+      <c r="C833">
+        <v>10202.77</v>
+      </c>
+      <c r="D833">
+        <v>172.18</v>
+      </c>
+      <c r="E833">
+        <v>4406.25</v>
+      </c>
+      <c r="F833">
+        <v>3093.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F833"/>
+  <dimension ref="A1:F834"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17050,6 +17050,26 @@
         <v>3093.02</v>
       </c>
     </row>
+    <row r="834" spans="1:6">
+      <c r="A834" s="1">
+        <v>832</v>
+      </c>
+      <c r="B834" s="2">
+        <v>46165</v>
+      </c>
+      <c r="C834">
+        <v>10314.41</v>
+      </c>
+      <c r="D834">
+        <v>171.15</v>
+      </c>
+      <c r="E834">
+        <v>4407.14</v>
+      </c>
+      <c r="F834">
+        <v>3109.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F834"/>
+  <dimension ref="A1:F835"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17070,6 +17070,26 @@
         <v>3109.03</v>
       </c>
     </row>
+    <row r="835" spans="1:6">
+      <c r="A835" s="1">
+        <v>833</v>
+      </c>
+      <c r="B835" s="2">
+        <v>46168</v>
+      </c>
+      <c r="C835">
+        <v>10365.3</v>
+      </c>
+      <c r="D835">
+        <v>174.45</v>
+      </c>
+      <c r="E835">
+        <v>4457.9</v>
+      </c>
+      <c r="F835">
+        <v>3146.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F835"/>
+  <dimension ref="A1:F836"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17090,6 +17090,26 @@
         <v>3146.75</v>
       </c>
     </row>
+    <row r="836" spans="1:6">
+      <c r="A836" s="1">
+        <v>834</v>
+      </c>
+      <c r="B836" s="2">
+        <v>46169</v>
+      </c>
+      <c r="C836">
+        <v>10382.97</v>
+      </c>
+      <c r="D836">
+        <v>174.75</v>
+      </c>
+      <c r="E836">
+        <v>4465.5</v>
+      </c>
+      <c r="F836">
+        <v>3152.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F836"/>
+  <dimension ref="A1:F837"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17110,6 +17110,26 @@
         <v>3152.12</v>
       </c>
     </row>
+    <row r="837" spans="1:6">
+      <c r="A837" s="1">
+        <v>835</v>
+      </c>
+      <c r="B837" s="2">
+        <v>46170</v>
+      </c>
+      <c r="C837">
+        <v>10293.19</v>
+      </c>
+      <c r="D837">
+        <v>173.8</v>
+      </c>
+      <c r="E837">
+        <v>4438.23</v>
+      </c>
+      <c r="F837">
+        <v>3189.06</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F837"/>
+  <dimension ref="A1:F838"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17130,6 +17130,26 @@
         <v>3189.06</v>
       </c>
     </row>
+    <row r="838" spans="1:6">
+      <c r="A838" s="1">
+        <v>836</v>
+      </c>
+      <c r="B838" s="2">
+        <v>46171</v>
+      </c>
+      <c r="C838">
+        <v>10156.1</v>
+      </c>
+      <c r="D838">
+        <v>170.61</v>
+      </c>
+      <c r="E838">
+        <v>4403.42</v>
+      </c>
+      <c r="F838">
+        <v>3189.56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F838"/>
+  <dimension ref="A1:F839"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17150,6 +17150,26 @@
         <v>3189.56</v>
       </c>
     </row>
+    <row r="839" spans="1:6">
+      <c r="A839" s="1">
+        <v>837</v>
+      </c>
+      <c r="B839" s="2">
+        <v>46172</v>
+      </c>
+      <c r="C839">
+        <v>10091.47</v>
+      </c>
+      <c r="D839">
+        <v>166.74</v>
+      </c>
+      <c r="E839">
+        <v>4347.63</v>
+      </c>
+      <c r="F839">
+        <v>3103.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F839"/>
+  <dimension ref="A1:F840"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17170,6 +17170,26 @@
         <v>3103.17</v>
       </c>
     </row>
+    <row r="840" spans="1:6">
+      <c r="A840" s="1">
+        <v>838</v>
+      </c>
+      <c r="B840" s="2">
+        <v>46175</v>
+      </c>
+      <c r="C840">
+        <v>10457.9</v>
+      </c>
+      <c r="D840">
+        <v>174.34</v>
+      </c>
+      <c r="E840">
+        <v>4428.44</v>
+      </c>
+      <c r="F840">
+        <v>3183.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F840"/>
+  <dimension ref="A1:F841"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17190,6 +17190,26 @@
         <v>3183.87</v>
       </c>
     </row>
+    <row r="841" spans="1:6">
+      <c r="A841" s="1">
+        <v>839</v>
+      </c>
+      <c r="B841" s="2">
+        <v>46176</v>
+      </c>
+      <c r="C841">
+        <v>10379.54</v>
+      </c>
+      <c r="D841">
+        <v>176.49</v>
+      </c>
+      <c r="E841">
+        <v>4509.39</v>
+      </c>
+      <c r="F841">
+        <v>3168.01</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F841"/>
+  <dimension ref="A1:F842"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17210,6 +17210,26 @@
         <v>3168.01</v>
       </c>
     </row>
+    <row r="842" spans="1:6">
+      <c r="A842" s="1">
+        <v>840</v>
+      </c>
+      <c r="B842" s="2">
+        <v>46177</v>
+      </c>
+      <c r="C842">
+        <v>10620.3</v>
+      </c>
+      <c r="D842">
+        <v>179.82</v>
+      </c>
+      <c r="E842">
+        <v>4617.06</v>
+      </c>
+      <c r="F842">
+        <v>3251.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F842"/>
+  <dimension ref="A1:F843"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17230,6 +17230,26 @@
         <v>3251.75</v>
       </c>
     </row>
+    <row r="843" spans="1:6">
+      <c r="A843" s="1">
+        <v>841</v>
+      </c>
+      <c r="B843" s="2">
+        <v>46178</v>
+      </c>
+      <c r="C843">
+        <v>10616.63</v>
+      </c>
+      <c r="D843">
+        <v>177.58</v>
+      </c>
+      <c r="E843">
+        <v>4564.72</v>
+      </c>
+      <c r="F843">
+        <v>3231.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F843"/>
+  <dimension ref="A1:F844"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17250,6 +17250,26 @@
         <v>3231.85</v>
       </c>
     </row>
+    <row r="844" spans="1:6">
+      <c r="A844" s="1">
+        <v>842</v>
+      </c>
+      <c r="B844" s="2">
+        <v>46179</v>
+      </c>
+      <c r="C844">
+        <v>10622.15</v>
+      </c>
+      <c r="D844">
+        <v>173.57</v>
+      </c>
+      <c r="E844">
+        <v>4480.86</v>
+      </c>
+      <c r="F844">
+        <v>3132.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F844"/>
+  <dimension ref="A1:F846"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17270,6 +17270,46 @@
         <v>3132.12</v>
       </c>
     </row>
+    <row r="845" spans="1:6">
+      <c r="A845" s="1">
+        <v>843</v>
+      </c>
+      <c r="B845" s="2">
+        <v>46182</v>
+      </c>
+      <c r="C845">
+        <v>10282.13</v>
+      </c>
+      <c r="D845">
+        <v>171.14</v>
+      </c>
+      <c r="E845">
+        <v>4374.17</v>
+      </c>
+      <c r="F845">
+        <v>3102.2</v>
+      </c>
+    </row>
+    <row r="846" spans="1:6">
+      <c r="A846" s="1">
+        <v>844</v>
+      </c>
+      <c r="B846" s="2">
+        <v>46183</v>
+      </c>
+      <c r="C846">
+        <v>9964.290000000001</v>
+      </c>
+      <c r="D846">
+        <v>154.81</v>
+      </c>
+      <c r="E846">
+        <v>4068.19</v>
+      </c>
+      <c r="F846">
+        <v>2808.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F846"/>
+  <dimension ref="A1:F847"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17310,6 +17310,26 @@
         <v>2808.99</v>
       </c>
     </row>
+    <row r="847" spans="1:6">
+      <c r="A847" s="1">
+        <v>845</v>
+      </c>
+      <c r="B847" s="2">
+        <v>46184</v>
+      </c>
+      <c r="C847">
+        <v>9988.540000000001</v>
+      </c>
+      <c r="D847">
+        <v>158.33</v>
+      </c>
+      <c r="E847">
+        <v>4106.06</v>
+      </c>
+      <c r="F847">
+        <v>2894.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F847"/>
+  <dimension ref="A1:F848"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17330,6 +17330,26 @@
         <v>2894.33</v>
       </c>
     </row>
+    <row r="848" spans="1:6">
+      <c r="A848" s="1">
+        <v>846</v>
+      </c>
+      <c r="B848" s="2">
+        <v>46185</v>
+      </c>
+      <c r="C848">
+        <v>9642.75</v>
+      </c>
+      <c r="D848">
+        <v>149.02</v>
+      </c>
+      <c r="E848">
+        <v>3886.28</v>
+      </c>
+      <c r="F848">
+        <v>2864.42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F848"/>
+  <dimension ref="A1:F849"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17350,6 +17350,26 @@
         <v>2864.42</v>
       </c>
     </row>
+    <row r="849" spans="1:6">
+      <c r="A849" s="1">
+        <v>847</v>
+      </c>
+      <c r="B849" s="2">
+        <v>46189</v>
+      </c>
+      <c r="C849">
+        <v>9750.59</v>
+      </c>
+      <c r="D849">
+        <v>156.14</v>
+      </c>
+      <c r="E849">
+        <v>3969.23</v>
+      </c>
+      <c r="F849">
+        <v>2990.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F849"/>
+  <dimension ref="A1:F850"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17370,6 +17370,26 @@
         <v>2990.9</v>
       </c>
     </row>
+    <row r="850" spans="1:6">
+      <c r="A850" s="1">
+        <v>848</v>
+      </c>
+      <c r="B850" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C850">
+        <v>10101.08</v>
+      </c>
+      <c r="D850">
+        <v>163.95</v>
+      </c>
+      <c r="E850">
+        <v>4172.45</v>
+      </c>
+      <c r="F850">
+        <v>3131.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F850"/>
+  <dimension ref="A1:F851"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17390,6 +17390,26 @@
         <v>3131.07</v>
       </c>
     </row>
+    <row r="851" spans="1:6">
+      <c r="A851" s="1">
+        <v>849</v>
+      </c>
+      <c r="B851" s="2">
+        <v>46191</v>
+      </c>
+      <c r="C851">
+        <v>10140.99</v>
+      </c>
+      <c r="D851">
+        <v>164.6</v>
+      </c>
+      <c r="E851">
+        <v>4242.76</v>
+      </c>
+      <c r="F851">
+        <v>3197.27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F851"/>
+  <dimension ref="A1:F852"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17410,6 +17410,26 @@
         <v>3197.27</v>
       </c>
     </row>
+    <row r="852" spans="1:6">
+      <c r="A852" s="1">
+        <v>850</v>
+      </c>
+      <c r="B852" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C852">
+        <v>10240.46</v>
+      </c>
+      <c r="D852">
+        <v>164.64</v>
+      </c>
+      <c r="E852">
+        <v>4217.08</v>
+      </c>
+      <c r="F852">
+        <v>3184.04</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F852"/>
+  <dimension ref="A1:F853"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17430,6 +17430,26 @@
         <v>3184.04</v>
       </c>
     </row>
+    <row r="853" spans="1:6">
+      <c r="A853" s="1">
+        <v>851</v>
+      </c>
+      <c r="B853" s="2">
+        <v>46193</v>
+      </c>
+      <c r="C853">
+        <v>10002.05</v>
+      </c>
+      <c r="D853">
+        <v>159.97</v>
+      </c>
+      <c r="E853">
+        <v>4049.32</v>
+      </c>
+      <c r="F853">
+        <v>3071.81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F853"/>
+  <dimension ref="A1:F854"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17450,6 +17450,26 @@
         <v>3071.81</v>
       </c>
     </row>
+    <row r="854" spans="1:6">
+      <c r="A854" s="1">
+        <v>852</v>
+      </c>
+      <c r="B854" s="2">
+        <v>46196</v>
+      </c>
+      <c r="C854">
+        <v>9844.27</v>
+      </c>
+      <c r="D854">
+        <v>153.36</v>
+      </c>
+      <c r="E854">
+        <v>3941.6</v>
+      </c>
+      <c r="F854">
+        <v>2957.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F854"/>
+  <dimension ref="A1:F855"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17470,6 +17470,26 @@
         <v>2957.38</v>
       </c>
     </row>
+    <row r="855" spans="1:6">
+      <c r="A855" s="1">
+        <v>853</v>
+      </c>
+      <c r="B855" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C855">
+        <v>10068.85</v>
+      </c>
+      <c r="D855">
+        <v>159.18</v>
+      </c>
+      <c r="E855">
+        <v>4040.06</v>
+      </c>
+      <c r="F855">
+        <v>3037.24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F855"/>
+  <dimension ref="A1:F856"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17490,6 +17490,26 @@
         <v>3037.24</v>
       </c>
     </row>
+    <row r="856" spans="1:6">
+      <c r="A856" s="1">
+        <v>854</v>
+      </c>
+      <c r="B856" s="2">
+        <v>46198</v>
+      </c>
+      <c r="C856">
+        <v>9941.870000000001</v>
+      </c>
+      <c r="D856">
+        <v>149.51</v>
+      </c>
+      <c r="E856">
+        <v>3957.04</v>
+      </c>
+      <c r="F856">
+        <v>2966.58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F856"/>
+  <dimension ref="A1:F857"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17510,6 +17510,26 @@
         <v>2966.58</v>
       </c>
     </row>
+    <row r="857" spans="1:6">
+      <c r="A857" s="1">
+        <v>855</v>
+      </c>
+      <c r="B857" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C857">
+        <v>9786.299999999999</v>
+      </c>
+      <c r="D857">
+        <v>147.36</v>
+      </c>
+      <c r="E857">
+        <v>3863.99</v>
+      </c>
+      <c r="F857">
+        <v>2874.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F857"/>
+  <dimension ref="A1:F858"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17530,6 +17530,26 @@
         <v>2874.28</v>
       </c>
     </row>
+    <row r="858" spans="1:6">
+      <c r="A858" s="1">
+        <v>856</v>
+      </c>
+      <c r="B858" s="2">
+        <v>46200</v>
+      </c>
+      <c r="C858">
+        <v>9914.74</v>
+      </c>
+      <c r="D858">
+        <v>142.13</v>
+      </c>
+      <c r="E858">
+        <v>3983.93</v>
+      </c>
+      <c r="F858">
+        <v>2980.52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F858"/>
+  <dimension ref="A1:F859"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17550,6 +17550,26 @@
         <v>2980.52</v>
       </c>
     </row>
+    <row r="859" spans="1:6">
+      <c r="A859" s="1">
+        <v>857</v>
+      </c>
+      <c r="B859" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C859">
+        <v>10179.49</v>
+      </c>
+      <c r="D859">
+        <v>145.94</v>
+      </c>
+      <c r="E859">
+        <v>4032.25</v>
+      </c>
+      <c r="F859">
+        <v>2999.81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F859"/>
+  <dimension ref="A1:F860"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17570,6 +17570,26 @@
         <v>2999.81</v>
       </c>
     </row>
+    <row r="860" spans="1:6">
+      <c r="A860" s="1">
+        <v>858</v>
+      </c>
+      <c r="B860" s="2">
+        <v>46204</v>
+      </c>
+      <c r="C860">
+        <v>10132.26</v>
+      </c>
+      <c r="D860">
+        <v>145.21</v>
+      </c>
+      <c r="E860">
+        <v>3996.08</v>
+      </c>
+      <c r="F860">
+        <v>3049.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F860"/>
+  <dimension ref="A1:F861"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17590,6 +17590,26 @@
         <v>3049.91</v>
       </c>
     </row>
+    <row r="861" spans="1:6">
+      <c r="A861" s="1">
+        <v>859</v>
+      </c>
+      <c r="B861" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C861">
+        <v>10130.68</v>
+      </c>
+      <c r="D861">
+        <v>147.94</v>
+      </c>
+      <c r="E861">
+        <v>3943.02</v>
+      </c>
+      <c r="F861">
+        <v>3069.86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F861"/>
+  <dimension ref="A1:F862"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17610,6 +17610,26 @@
         <v>3069.86</v>
       </c>
     </row>
+    <row r="862" spans="1:6">
+      <c r="A862" s="1">
+        <v>860</v>
+      </c>
+      <c r="B862" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C862">
+        <v>10246.05</v>
+      </c>
+      <c r="D862">
+        <v>145.94</v>
+      </c>
+      <c r="E862">
+        <v>3932.11</v>
+      </c>
+      <c r="F862">
+        <v>3018.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F862"/>
+  <dimension ref="A1:F863"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17630,6 +17630,26 @@
         <v>3018.48</v>
       </c>
     </row>
+    <row r="863" spans="1:6">
+      <c r="A863" s="1">
+        <v>861</v>
+      </c>
+      <c r="B863" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C863">
+        <v>10252.33</v>
+      </c>
+      <c r="D863">
+        <v>148.08</v>
+      </c>
+      <c r="E863">
+        <v>4016.19</v>
+      </c>
+      <c r="F863">
+        <v>3116.76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F863"/>
+  <dimension ref="A1:F864"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17650,6 +17650,26 @@
         <v>3116.76</v>
       </c>
     </row>
+    <row r="864" spans="1:6">
+      <c r="A864" s="1">
+        <v>862</v>
+      </c>
+      <c r="B864" s="2">
+        <v>46210</v>
+      </c>
+      <c r="C864">
+        <v>10438.59</v>
+      </c>
+      <c r="D864">
+        <v>156.06</v>
+      </c>
+      <c r="E864">
+        <v>4133.42</v>
+      </c>
+      <c r="F864">
+        <v>3200.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F864"/>
+  <dimension ref="A1:F865"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17670,6 +17670,26 @@
         <v>3200.9</v>
       </c>
     </row>
+    <row r="865" spans="1:6">
+      <c r="A865" s="1">
+        <v>863</v>
+      </c>
+      <c r="B865" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C865">
+        <v>10134.97</v>
+      </c>
+      <c r="D865">
+        <v>151.92</v>
+      </c>
+      <c r="E865">
+        <v>3958.34</v>
+      </c>
+      <c r="F865">
+        <v>3090.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F865"/>
+  <dimension ref="A1:F866"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17690,6 +17690,26 @@
         <v>3090.09</v>
       </c>
     </row>
+    <row r="866" spans="1:6">
+      <c r="A866" s="1">
+        <v>864</v>
+      </c>
+      <c r="B866" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C866">
+        <v>10208.3</v>
+      </c>
+      <c r="D866">
+        <v>148.96</v>
+      </c>
+      <c r="E866">
+        <v>4040.9</v>
+      </c>
+      <c r="F866">
+        <v>3145.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F866"/>
+  <dimension ref="A1:F867"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17710,6 +17710,26 @@
         <v>3145.91</v>
       </c>
     </row>
+    <row r="867" spans="1:6">
+      <c r="A867" s="1">
+        <v>865</v>
+      </c>
+      <c r="B867" s="2">
+        <v>46213</v>
+      </c>
+      <c r="C867">
+        <v>9926.43</v>
+      </c>
+      <c r="D867">
+        <v>142.62</v>
+      </c>
+      <c r="E867">
+        <v>3867.97</v>
+      </c>
+      <c r="F867">
+        <v>2979</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F867"/>
+  <dimension ref="A1:F868"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17730,6 +17730,26 @@
         <v>2979</v>
       </c>
     </row>
+    <row r="868" spans="1:6">
+      <c r="A868" s="1">
+        <v>866</v>
+      </c>
+      <c r="B868" s="2">
+        <v>46214</v>
+      </c>
+      <c r="C868">
+        <v>10180.1</v>
+      </c>
+      <c r="D868">
+        <v>144.99</v>
+      </c>
+      <c r="E868">
+        <v>3990.18</v>
+      </c>
+      <c r="F868">
+        <v>3108.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F868"/>
+  <dimension ref="A1:F869"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17750,6 +17750,26 @@
         <v>3108.14</v>
       </c>
     </row>
+    <row r="869" spans="1:6">
+      <c r="A869" s="1">
+        <v>867</v>
+      </c>
+      <c r="B869" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C869">
+        <v>10097.97</v>
+      </c>
+      <c r="D869">
+        <v>146.19</v>
+      </c>
+      <c r="E869">
+        <v>3986.94</v>
+      </c>
+      <c r="F869">
+        <v>3139.52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F869"/>
+  <dimension ref="A1:F870"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17770,6 +17770,26 @@
         <v>3139.52</v>
       </c>
     </row>
+    <row r="870" spans="1:6">
+      <c r="A870" s="1">
+        <v>868</v>
+      </c>
+      <c r="B870" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C870">
+        <v>10064.63</v>
+      </c>
+      <c r="D870">
+        <v>145.47</v>
+      </c>
+      <c r="E870">
+        <v>4050.51</v>
+      </c>
+      <c r="F870">
+        <v>3170.18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F870"/>
+  <dimension ref="A1:F871"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17790,6 +17790,26 @@
         <v>3170.18</v>
       </c>
     </row>
+    <row r="871" spans="1:6">
+      <c r="A871" s="1">
+        <v>869</v>
+      </c>
+      <c r="B871" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C871">
+        <v>10214.7</v>
+      </c>
+      <c r="D871">
+        <v>145.07</v>
+      </c>
+      <c r="E871">
+        <v>4087.01</v>
+      </c>
+      <c r="F871">
+        <v>3210.66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F871"/>
+  <dimension ref="A1:F872"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17810,6 +17810,26 @@
         <v>3210.66</v>
       </c>
     </row>
+    <row r="872" spans="1:6">
+      <c r="A872" s="1">
+        <v>870</v>
+      </c>
+      <c r="B872" s="2">
+        <v>46220</v>
+      </c>
+      <c r="C872">
+        <v>10228.55</v>
+      </c>
+      <c r="D872">
+        <v>145.92</v>
+      </c>
+      <c r="E872">
+        <v>4144.85</v>
+      </c>
+      <c r="F872">
+        <v>3316.56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F872"/>
+  <dimension ref="A1:F873"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17830,6 +17830,26 @@
         <v>3316.56</v>
       </c>
     </row>
+    <row r="873" spans="1:6">
+      <c r="A873" s="1">
+        <v>871</v>
+      </c>
+      <c r="B873" s="2">
+        <v>46221</v>
+      </c>
+      <c r="C873">
+        <v>10066.04</v>
+      </c>
+      <c r="D873">
+        <v>142.41</v>
+      </c>
+      <c r="E873">
+        <v>4153.28</v>
+      </c>
+      <c r="F873">
+        <v>3186.01</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F873"/>
+  <dimension ref="A1:F874"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17850,6 +17850,26 @@
         <v>3186.01</v>
       </c>
     </row>
+    <row r="874" spans="1:6">
+      <c r="A874" s="1">
+        <v>872</v>
+      </c>
+      <c r="B874" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C874">
+        <v>10059.94</v>
+      </c>
+      <c r="D874">
+        <v>139.22</v>
+      </c>
+      <c r="E874">
+        <v>3957.53</v>
+      </c>
+      <c r="F874">
+        <v>3120.32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F874"/>
+  <dimension ref="A1:F875"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17870,6 +17870,26 @@
         <v>3120.32</v>
       </c>
     </row>
+    <row r="875" spans="1:6">
+      <c r="A875" s="1">
+        <v>873</v>
+      </c>
+      <c r="B875" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C875">
+        <v>10111.24</v>
+      </c>
+      <c r="D875">
+        <v>143.48</v>
+      </c>
+      <c r="E875">
+        <v>4005.8</v>
+      </c>
+      <c r="F875">
+        <v>3204.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F875"/>
+  <dimension ref="A1:F876"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17890,6 +17890,26 @@
         <v>3204.44</v>
       </c>
     </row>
+    <row r="876" spans="1:6">
+      <c r="A876" s="1">
+        <v>874</v>
+      </c>
+      <c r="B876" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C876">
+        <v>10224.14</v>
+      </c>
+      <c r="D876">
+        <v>148.58</v>
+      </c>
+      <c r="E876">
+        <v>4091.5</v>
+      </c>
+      <c r="F876">
+        <v>3218.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F876"/>
+  <dimension ref="A1:F877"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17910,6 +17910,26 @@
         <v>3218.78</v>
       </c>
     </row>
+    <row r="877" spans="1:6">
+      <c r="A877" s="1">
+        <v>875</v>
+      </c>
+      <c r="B877" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C877">
+        <v>10474.07</v>
+      </c>
+      <c r="D877">
+        <v>149.58</v>
+      </c>
+      <c r="E877">
+        <v>4149.57</v>
+      </c>
+      <c r="F877">
+        <v>3314.69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F877"/>
+  <dimension ref="A1:F878"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17930,6 +17930,26 @@
         <v>3314.69</v>
       </c>
     </row>
+    <row r="878" spans="1:6">
+      <c r="A878" s="1">
+        <v>876</v>
+      </c>
+      <c r="B878" s="2">
+        <v>46228</v>
+      </c>
+      <c r="C878">
+        <v>10147.63</v>
+      </c>
+      <c r="D878">
+        <v>147.16</v>
+      </c>
+      <c r="E878">
+        <v>4028.42</v>
+      </c>
+      <c r="F878">
+        <v>3168.42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F878"/>
+  <dimension ref="A1:F879"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17950,6 +17950,26 @@
         <v>3168.42</v>
       </c>
     </row>
+    <row r="879" spans="1:6">
+      <c r="A879" s="1">
+        <v>877</v>
+      </c>
+      <c r="B879" s="2">
+        <v>46231</v>
+      </c>
+      <c r="C879">
+        <v>10202.05</v>
+      </c>
+      <c r="D879">
+        <v>146.3</v>
+      </c>
+      <c r="E879">
+        <v>4015.05</v>
+      </c>
+      <c r="F879">
+        <v>3150.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F879"/>
+  <dimension ref="A1:F880"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17970,6 +17970,26 @@
         <v>3150.44</v>
       </c>
     </row>
+    <row r="880" spans="1:6">
+      <c r="A880" s="1">
+        <v>878</v>
+      </c>
+      <c r="B880" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C880">
+        <v>10310.56</v>
+      </c>
+      <c r="D880">
+        <v>149.37</v>
+      </c>
+      <c r="E880">
+        <v>4119.79</v>
+      </c>
+      <c r="F880">
+        <v>3243.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F880"/>
+  <dimension ref="A1:F881"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -17990,6 +17990,26 @@
         <v>3243.33</v>
       </c>
     </row>
+    <row r="881" spans="1:6">
+      <c r="A881" s="1">
+        <v>879</v>
+      </c>
+      <c r="B881" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C881">
+        <v>10262.18</v>
+      </c>
+      <c r="D881">
+        <v>145.86</v>
+      </c>
+      <c r="E881">
+        <v>4094.59</v>
+      </c>
+      <c r="F881">
+        <v>3230.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F881"/>
+  <dimension ref="A1:F882"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18010,6 +18010,26 @@
         <v>3230.95</v>
       </c>
     </row>
+    <row r="882" spans="1:6">
+      <c r="A882" s="1">
+        <v>880</v>
+      </c>
+      <c r="B882" s="2">
+        <v>46234</v>
+      </c>
+      <c r="C882">
+        <v>10272.06</v>
+      </c>
+      <c r="D882">
+        <v>147.36</v>
+      </c>
+      <c r="E882">
+        <v>4099.99</v>
+      </c>
+      <c r="F882">
+        <v>3222.94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F882"/>
+  <dimension ref="A1:F883"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18030,6 +18030,26 @@
         <v>3222.94</v>
       </c>
     </row>
+    <row r="883" spans="1:6">
+      <c r="A883" s="1">
+        <v>881</v>
+      </c>
+      <c r="B883" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C883">
+        <v>10502.97</v>
+      </c>
+      <c r="D883">
+        <v>148.32</v>
+      </c>
+      <c r="E883">
+        <v>4140.33</v>
+      </c>
+      <c r="F883">
+        <v>3280</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F883"/>
+  <dimension ref="A1:F884"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18050,6 +18050,26 @@
         <v>3280</v>
       </c>
     </row>
+    <row r="884" spans="1:6">
+      <c r="A884" s="1">
+        <v>882</v>
+      </c>
+      <c r="B884" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C884">
+        <v>10365.54</v>
+      </c>
+      <c r="D884">
+        <v>148.6</v>
+      </c>
+      <c r="E884">
+        <v>4185.76</v>
+      </c>
+      <c r="F884">
+        <v>3286.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F884"/>
+  <dimension ref="A1:F885"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18070,6 +18070,26 @@
         <v>3286.05</v>
       </c>
     </row>
+    <row r="885" spans="1:6">
+      <c r="A885" s="1">
+        <v>883</v>
+      </c>
+      <c r="B885" s="2">
+        <v>46239</v>
+      </c>
+      <c r="C885">
+        <v>10506.86</v>
+      </c>
+      <c r="D885">
+        <v>151.19</v>
+      </c>
+      <c r="E885">
+        <v>4216.8</v>
+      </c>
+      <c r="F885">
+        <v>3254.06</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F885"/>
+  <dimension ref="A1:F886"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18090,6 +18090,26 @@
         <v>3254.06</v>
       </c>
     </row>
+    <row r="886" spans="1:6">
+      <c r="A886" s="1">
+        <v>884</v>
+      </c>
+      <c r="B886" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C886">
+        <v>10626.82</v>
+      </c>
+      <c r="D886">
+        <v>152.95</v>
+      </c>
+      <c r="E886">
+        <v>4448.01</v>
+      </c>
+      <c r="F886">
+        <v>3423.24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F886"/>
+  <dimension ref="A1:F887"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18110,6 +18110,26 @@
         <v>3423.24</v>
       </c>
     </row>
+    <row r="887" spans="1:6">
+      <c r="A887" s="1">
+        <v>885</v>
+      </c>
+      <c r="B887" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C887">
+        <v>11010</v>
+      </c>
+      <c r="D887">
+        <v>160.35</v>
+      </c>
+      <c r="E887">
+        <v>4507.54</v>
+      </c>
+      <c r="F887">
+        <v>3545.42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F887"/>
+  <dimension ref="A1:F888"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18130,6 +18130,26 @@
         <v>3545.42</v>
       </c>
     </row>
+    <row r="888" spans="1:6">
+      <c r="A888" s="1">
+        <v>886</v>
+      </c>
+      <c r="B888" s="2">
+        <v>46242</v>
+      </c>
+      <c r="C888">
+        <v>11274.43</v>
+      </c>
+      <c r="D888">
+        <v>163.09</v>
+      </c>
+      <c r="E888">
+        <v>4565.01</v>
+      </c>
+      <c r="F888">
+        <v>3626.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F888"/>
+  <dimension ref="A1:F889"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18150,6 +18150,26 @@
         <v>3626.15</v>
       </c>
     </row>
+    <row r="889" spans="1:6">
+      <c r="A889" s="1">
+        <v>887</v>
+      </c>
+      <c r="B889" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C889">
+        <v>11514.54</v>
+      </c>
+      <c r="D889">
+        <v>170.82</v>
+      </c>
+      <c r="E889">
+        <v>4643.08</v>
+      </c>
+      <c r="F889">
+        <v>3658.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F889"/>
+  <dimension ref="A1:F890"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18170,6 +18170,26 @@
         <v>3658.95</v>
       </c>
     </row>
+    <row r="890" spans="1:6">
+      <c r="A890" s="1">
+        <v>888</v>
+      </c>
+      <c r="B890" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C890">
+        <v>11452.83</v>
+      </c>
+      <c r="D890">
+        <v>169.32</v>
+      </c>
+      <c r="E890">
+        <v>4617.2</v>
+      </c>
+      <c r="F890">
+        <v>3618.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F890"/>
+  <dimension ref="A1:F891"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18190,6 +18190,26 @@
         <v>3618.5</v>
       </c>
     </row>
+    <row r="891" spans="1:6">
+      <c r="A891" s="1">
+        <v>889</v>
+      </c>
+      <c r="B891" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C891">
+        <v>11696.69</v>
+      </c>
+      <c r="D891">
+        <v>173.94</v>
+      </c>
+      <c r="E891">
+        <v>4692.18</v>
+      </c>
+      <c r="F891">
+        <v>3662.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F891"/>
+  <dimension ref="A1:F892"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18210,6 +18210,26 @@
         <v>3662.7</v>
       </c>
     </row>
+    <row r="892" spans="1:6">
+      <c r="A892" s="1">
+        <v>890</v>
+      </c>
+      <c r="B892" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C892">
+        <v>11927.24</v>
+      </c>
+      <c r="D892">
+        <v>178.51</v>
+      </c>
+      <c r="E892">
+        <v>4784.75</v>
+      </c>
+      <c r="F892">
+        <v>3729.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F892"/>
+  <dimension ref="A1:F893"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18230,6 +18230,26 @@
         <v>3729.75</v>
       </c>
     </row>
+    <row r="893" spans="1:6">
+      <c r="A893" s="1">
+        <v>891</v>
+      </c>
+      <c r="B893" s="2">
+        <v>46249</v>
+      </c>
+      <c r="C893">
+        <v>11886.6</v>
+      </c>
+      <c r="D893">
+        <v>176.56</v>
+      </c>
+      <c r="E893">
+        <v>4712.78</v>
+      </c>
+      <c r="F893">
+        <v>3600.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F893"/>
+  <dimension ref="A1:F894"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18250,6 +18250,26 @@
         <v>3600.23</v>
       </c>
     </row>
+    <row r="894" spans="1:6">
+      <c r="A894" s="1">
+        <v>892</v>
+      </c>
+      <c r="B894" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C894">
+        <v>12000.87</v>
+      </c>
+      <c r="D894">
+        <v>176.58</v>
+      </c>
+      <c r="E894">
+        <v>4751.89</v>
+      </c>
+      <c r="F894">
+        <v>3608.16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F894"/>
+  <dimension ref="A1:F895"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18270,6 +18270,26 @@
         <v>3608.16</v>
       </c>
     </row>
+    <row r="895" spans="1:6">
+      <c r="A895" s="1">
+        <v>893</v>
+      </c>
+      <c r="B895" s="2">
+        <v>46253</v>
+      </c>
+      <c r="C895">
+        <v>12063.52</v>
+      </c>
+      <c r="D895">
+        <v>179.65</v>
+      </c>
+      <c r="E895">
+        <v>4841.51</v>
+      </c>
+      <c r="F895">
+        <v>3647.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F895"/>
+  <dimension ref="A1:F896"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18290,6 +18290,26 @@
         <v>3647.7</v>
       </c>
     </row>
+    <row r="896" spans="1:6">
+      <c r="A896" s="1">
+        <v>894</v>
+      </c>
+      <c r="B896" s="2">
+        <v>46254</v>
+      </c>
+      <c r="C896">
+        <v>12052.24</v>
+      </c>
+      <c r="D896">
+        <v>178.16</v>
+      </c>
+      <c r="E896">
+        <v>4796.81</v>
+      </c>
+      <c r="F896">
+        <v>3604.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F896"/>
+  <dimension ref="A1:F897"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18310,6 +18310,26 @@
         <v>3604.72</v>
       </c>
     </row>
+    <row r="897" spans="1:6">
+      <c r="A897" s="1">
+        <v>895</v>
+      </c>
+      <c r="B897" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C897">
+        <v>11954.33</v>
+      </c>
+      <c r="D897">
+        <v>169.79</v>
+      </c>
+      <c r="E897">
+        <v>4704.34</v>
+      </c>
+      <c r="F897">
+        <v>3515.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F897"/>
+  <dimension ref="A1:F898"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18330,6 +18330,26 @@
         <v>3515.26</v>
       </c>
     </row>
+    <row r="898" spans="1:6">
+      <c r="A898" s="1">
+        <v>896</v>
+      </c>
+      <c r="B898" s="2">
+        <v>46256</v>
+      </c>
+      <c r="C898">
+        <v>11951.42</v>
+      </c>
+      <c r="D898">
+        <v>177.94</v>
+      </c>
+      <c r="E898">
+        <v>4826.08</v>
+      </c>
+      <c r="F898">
+        <v>3564.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F898"/>
+  <dimension ref="A1:F899"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18350,6 +18350,26 @@
         <v>3564.14</v>
       </c>
     </row>
+    <row r="899" spans="1:6">
+      <c r="A899" s="1">
+        <v>897</v>
+      </c>
+      <c r="B899" s="2">
+        <v>46259</v>
+      </c>
+      <c r="C899">
+        <v>12269.78</v>
+      </c>
+      <c r="D899">
+        <v>186.13</v>
+      </c>
+      <c r="E899">
+        <v>5058.16</v>
+      </c>
+      <c r="F899">
+        <v>3644.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F899"/>
+  <dimension ref="A1:F900"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18370,6 +18370,26 @@
         <v>3644.3</v>
       </c>
     </row>
+    <row r="900" spans="1:6">
+      <c r="A900" s="1">
+        <v>898</v>
+      </c>
+      <c r="B900" s="2">
+        <v>46260</v>
+      </c>
+      <c r="C900">
+        <v>12664.57</v>
+      </c>
+      <c r="D900">
+        <v>186.61</v>
+      </c>
+      <c r="E900">
+        <v>5135.26</v>
+      </c>
+      <c r="F900">
+        <v>3691.54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F900"/>
+  <dimension ref="A1:F901"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18390,6 +18390,26 @@
         <v>3691.54</v>
       </c>
     </row>
+    <row r="901" spans="1:6">
+      <c r="A901" s="1">
+        <v>899</v>
+      </c>
+      <c r="B901" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C901">
+        <v>12506.61</v>
+      </c>
+      <c r="D901">
+        <v>183.9</v>
+      </c>
+      <c r="E901">
+        <v>4974.92</v>
+      </c>
+      <c r="F901">
+        <v>3582.39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F901"/>
+  <dimension ref="A1:F902"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18410,6 +18410,26 @@
         <v>3582.39</v>
       </c>
     </row>
+    <row r="902" spans="1:6">
+      <c r="A902" s="1">
+        <v>900</v>
+      </c>
+      <c r="B902" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C902">
+        <v>12799.09</v>
+      </c>
+      <c r="D902">
+        <v>189.29</v>
+      </c>
+      <c r="E902">
+        <v>5131.52</v>
+      </c>
+      <c r="F902">
+        <v>3711.36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F902"/>
+  <dimension ref="A1:F903"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18430,6 +18430,26 @@
         <v>3711.36</v>
       </c>
     </row>
+    <row r="903" spans="1:6">
+      <c r="A903" s="1">
+        <v>901</v>
+      </c>
+      <c r="B903" s="2">
+        <v>46263</v>
+      </c>
+      <c r="C903">
+        <v>12574.32</v>
+      </c>
+      <c r="D903">
+        <v>188.44</v>
+      </c>
+      <c r="E903">
+        <v>5012.44</v>
+      </c>
+      <c r="F903">
+        <v>3599.64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F903"/>
+  <dimension ref="A1:F904"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18450,6 +18450,26 @@
         <v>3599.64</v>
       </c>
     </row>
+    <row r="904" spans="1:6">
+      <c r="A904" s="1">
+        <v>902</v>
+      </c>
+      <c r="B904" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C904">
+        <v>12671.47</v>
+      </c>
+      <c r="D904">
+        <v>195.12</v>
+      </c>
+      <c r="E904">
+        <v>5232.02</v>
+      </c>
+      <c r="F904">
+        <v>4009.94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/cb_metalls.xlsx
+++ b/LME/parser_beta_2.0/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F904"/>
+  <dimension ref="A1:F905"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -18470,6 +18470,26 @@
         <v>4009.94</v>
       </c>
     </row>
+    <row r="905" spans="1:6">
+      <c r="A905" s="1">
+        <v>903</v>
+      </c>
+      <c r="B905" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C905">
+        <v>12726.29</v>
+      </c>
+      <c r="D905">
+        <v>195.97</v>
+      </c>
+      <c r="E905">
+        <v>5254.66</v>
+      </c>
+      <c r="F905">
+        <v>4027.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
